--- a/templates/000_pm_suite/프로젝트 방법론_구성표_V1.0.xlsx
+++ b/templates/000_pm_suite/프로젝트 방법론_구성표_V1.0.xlsx
@@ -49,7 +49,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="288">
   <si>
-    <t>프로젝트 관리 및 개발방법론</t>
+    <t>프로젝트 관리 및 개발방법론 [주식회사 엠파시 · 한빛글로벌 SyncGuard AI 표준]</t>
   </si>
   <si>
     <t>구분</t>

--- a/templates/000_pm_suite/프로젝트 방법론_구성표_V1.0.xlsx
+++ b/templates/000_pm_suite/프로젝트 방법론_구성표_V1.0.xlsx
@@ -49,7 +49,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="288">
   <si>
-    <t>프로젝트 관리 및 개발방법론 [주식회사 엠파시 · 한빛글로벌 SyncGuard AI 표준]</t>
+    <t>프로젝트 관리 및 개발방법론 [주식회사 엠파시 · 한빛글로벌 SyncFlow AI 표준]</t>
   </si>
   <si>
     <t>구분</t>
@@ -334,7 +334,7 @@
     <t>제안서초안</t>
   </si>
   <si>
-    <t>디자인시안</t>
+    <t>디자인계약·도서</t>
   </si>
   <si>
     <t>제안서융합</t>
@@ -545,13 +545,13 @@
 선임디자이너</t>
   </si>
   <si>
-    <t>디자인시안작업</t>
-  </si>
-  <si>
-    <t>디자인시안 (디자인파일)</t>
-  </si>
-  <si>
-    <t>디자인시안검토</t>
+    <t>디자인계약·도서작업</t>
+  </si>
+  <si>
+    <t>디자인계약·도서 (디자인파일)</t>
+  </si>
+  <si>
+    <t>디자인계약·도서검토</t>
   </si>
   <si>
     <t>디자인팀장</t>
@@ -666,7 +666,7 @@
     <t>디자인</t>
   </si>
   <si>
-    <t>상세페이지 디자인 작업</t>
+    <t>기술시방서 디자인 작업</t>
   </si>
   <si>
     <t>디자인소스(디자인 파일)</t>
